--- a/data/publications/monthly-rbi-bulletin/occasional-series/table-48-combined-receipts-and-disbursements-of-the-central-and-state-governments.xlsx
+++ b/data/publications/monthly-rbi-bulletin/occasional-series/table-48-combined-receipts-and-disbursements-of-the-central-and-state-governments.xlsx
@@ -491,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH54"/>
+  <dimension ref="A1:AH55"/>
   <cols>
     <col min="1" max="1" width="4.95147066666667" customWidth="1"/>
     <col min="2" max="2" width="37.015556" customWidth="1"/>
@@ -499,7 +499,7 @@
     <col min="7" max="7" width="20.8542226666667" customWidth="1"/>
     <col min="8" max="8" width="20.839012" customWidth="1"/>
     <col min="9" max="34" width="20.8466173333333" customWidth="1"/>
-    <col min="35" max="35" width="160128e-6" customWidth="1"/>
+    <col min="35" max="35" width="4.95147066666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -5086,6 +5086,7 @@
       <c r="E54" s="19"/>
       <c r="F54" s="19"/>
     </row>
+    <row r="55" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:G2"/>
